--- a/assets/files/sistem_penggajian.xlsx
+++ b/assets/files/sistem_penggajian.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\kursus\assets\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1FBE5D9-408E-4096-A27D-871C71394919}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1097D55-F3E8-4C5B-A632-0A3E92749EA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" activeTab="1" xr2:uid="{DA57F0ED-037E-4465-B006-D110F2FD2381}"/>
+    <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{DA57F0ED-037E-4465-B006-D110F2FD2381}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,15 +21,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -94,30 +85,6 @@
     <t>K008</t>
   </si>
   <si>
-    <t>Andi </t>
-  </si>
-  <si>
-    <t>Budi </t>
-  </si>
-  <si>
-    <t>Cici </t>
-  </si>
-  <si>
-    <t>Dodi </t>
-  </si>
-  <si>
-    <t>Eka </t>
-  </si>
-  <si>
-    <t>Fani </t>
-  </si>
-  <si>
-    <t>Gita </t>
-  </si>
-  <si>
-    <t>Hadi </t>
-  </si>
-  <si>
     <t>VI</t>
   </si>
   <si>
@@ -128,6 +95,30 @@
   </si>
   <si>
     <t>TABEL REFERENSI GAJI</t>
+  </si>
+  <si>
+    <t>Cici</t>
+  </si>
+  <si>
+    <t>Andi</t>
+  </si>
+  <si>
+    <t>Budi</t>
+  </si>
+  <si>
+    <t>Dodi</t>
+  </si>
+  <si>
+    <t>Eka</t>
+  </si>
+  <si>
+    <t>Fani</t>
+  </si>
+  <si>
+    <t>Gita</t>
+  </si>
+  <si>
+    <t>Hadi</t>
   </si>
 </sst>
 </file>
@@ -336,7 +327,7 @@
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -365,10 +356,10 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -715,25 +706,24 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7A32CDB-0F8E-45E8-AB06-32128E535B2A}">
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="21.7109375" style="2" customWidth="1"/>
     <col min="4" max="4" width="28.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" style="2"/>
-    <col min="6" max="6" width="16" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="5" max="5" width="26.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="16"/>
-    </row>
-    <row r="2" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="15"/>
+    </row>
+    <row r="2" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>10</v>
       </c>
@@ -747,9 +737,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>11</v>
@@ -758,13 +748,17 @@
         <v>4</v>
       </c>
       <c r="D3" s="5">
-        <f>IFERROR(VLOOKUP(C3,$A$14:$B$18,2,FALSE),"Golongan tidak ditemukan")</f>
+        <f>_xlfn.IFNA(VLOOKUP(C3,$A$14:$B$18,2,FALSE),"Golongan tidak ditemukan")</f>
         <v>9000000</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E3" s="2">
+        <f>IF(COUNTIF($A$14:$B$18,C3)=0,"Golongan '"&amp;C3&amp;"' tidak ditemukan",VLOOKUP(C3,$A$14:$B$18,2,FALSE))</f>
+        <v>9000000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>12</v>
@@ -773,13 +767,17 @@
         <v>3</v>
       </c>
       <c r="D4" s="5">
-        <f t="shared" ref="D4:D10" si="0">IFERROR(VLOOKUP(C4,$A$14:$B$18,2,FALSE),"Golongan tidak ditemukan")</f>
+        <f t="shared" ref="D4:D10" si="0">_xlfn.IFNA(VLOOKUP(C4,$A$14:$B$18,2,FALSE),"Golongan tidak ditemukan")</f>
         <v>7000000</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E4" s="2">
+        <f t="shared" ref="E4:E10" si="1">IF(COUNTIF($A$14:$B$18,C4)=0,"Golongan '"&amp;C4&amp;"' tidak ditemukan",VLOOKUP(C4,$A$14:$B$18,2,FALSE))</f>
+        <v>7000000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>13</v>
@@ -791,10 +789,14 @@
         <f t="shared" si="0"/>
         <v>15000000</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E5" s="2">
+        <f t="shared" si="1"/>
+        <v>15000000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>14</v>
@@ -806,10 +808,14 @@
         <f t="shared" si="0"/>
         <v>5000000</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E6" s="2">
+        <f t="shared" si="1"/>
+        <v>5000000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>15</v>
@@ -821,10 +827,14 @@
         <f t="shared" si="0"/>
         <v>12000000</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E7" s="2">
+        <f t="shared" si="1"/>
+        <v>12000000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>16</v>
@@ -836,45 +846,57 @@
         <f t="shared" si="0"/>
         <v>9000000</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E8" s="2">
+        <f t="shared" si="1"/>
+        <v>9000000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D9" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Golongan tidak ditemukan</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E9" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Golongan 'll' tidak ditemukan</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>18</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="8" t="str">
+        <v>19</v>
+      </c>
+      <c r="D10" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Golongan tidak ditemukan</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E10" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Golongan 'VI' tidak ditemukan</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="B12" s="16"/>
-    </row>
-    <row r="13" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="B12" s="15"/>
+    </row>
+    <row r="13" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
         <v>0</v>
       </c>
@@ -882,7 +904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
         <v>2</v>
       </c>
@@ -890,7 +912,7 @@
         <v>5000000</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
         <v>3</v>
       </c>
@@ -898,7 +920,7 @@
         <v>7000000</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
         <v>4</v>
       </c>

--- a/assets/files/sistem_penggajian.xlsx
+++ b/assets/files/sistem_penggajian.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\kursus\assets\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1097D55-F3E8-4C5B-A632-0A3E92749EA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28DAA2B9-D261-48AB-8EB4-ADF6DD3622D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{DA57F0ED-037E-4465-B006-D110F2FD2381}"/>
   </bookViews>
@@ -20,6 +20,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -380,9 +391,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -420,7 +431,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -526,7 +537,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -668,7 +679,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -706,7 +717,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7A32CDB-0F8E-45E8-AB06-32128E535B2A}">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="21.7109375" style="2" customWidth="1"/>
@@ -715,7 +726,7 @@
     <col min="6" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
         <v>21</v>
       </c>
@@ -723,7 +734,7 @@
       <c r="C1" s="16"/>
       <c r="D1" s="15"/>
     </row>
-    <row r="2" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>10</v>
       </c>
@@ -737,7 +748,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>24</v>
       </c>
@@ -751,12 +762,8 @@
         <f>_xlfn.IFNA(VLOOKUP(C3,$A$14:$B$18,2,FALSE),"Golongan tidak ditemukan")</f>
         <v>9000000</v>
       </c>
-      <c r="E3" s="2">
-        <f>IF(COUNTIF($A$14:$B$18,C3)=0,"Golongan '"&amp;C3&amp;"' tidak ditemukan",VLOOKUP(C3,$A$14:$B$18,2,FALSE))</f>
-        <v>9000000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>25</v>
       </c>
@@ -770,12 +777,8 @@
         <f t="shared" ref="D4:D10" si="0">_xlfn.IFNA(VLOOKUP(C4,$A$14:$B$18,2,FALSE),"Golongan tidak ditemukan")</f>
         <v>7000000</v>
       </c>
-      <c r="E4" s="2">
-        <f t="shared" ref="E4:E10" si="1">IF(COUNTIF($A$14:$B$18,C4)=0,"Golongan '"&amp;C4&amp;"' tidak ditemukan",VLOOKUP(C4,$A$14:$B$18,2,FALSE))</f>
-        <v>7000000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>23</v>
       </c>
@@ -789,12 +792,8 @@
         <f t="shared" si="0"/>
         <v>15000000</v>
       </c>
-      <c r="E5" s="2">
-        <f t="shared" si="1"/>
-        <v>15000000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>26</v>
       </c>
@@ -808,12 +807,8 @@
         <f t="shared" si="0"/>
         <v>5000000</v>
       </c>
-      <c r="E6" s="2">
-        <f t="shared" si="1"/>
-        <v>5000000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>27</v>
       </c>
@@ -827,12 +822,8 @@
         <f t="shared" si="0"/>
         <v>12000000</v>
       </c>
-      <c r="E7" s="2">
-        <f t="shared" si="1"/>
-        <v>12000000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>28</v>
       </c>
@@ -846,12 +837,8 @@
         <f t="shared" si="0"/>
         <v>9000000</v>
       </c>
-      <c r="E8" s="2">
-        <f t="shared" si="1"/>
-        <v>9000000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>29</v>
       </c>
@@ -865,12 +852,8 @@
         <f t="shared" si="0"/>
         <v>Golongan tidak ditemukan</v>
       </c>
-      <c r="E9" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Golongan 'll' tidak ditemukan</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>30</v>
       </c>
@@ -884,19 +867,15 @@
         <f t="shared" si="0"/>
         <v>Golongan tidak ditemukan</v>
       </c>
-      <c r="E10" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>Golongan 'VI' tidak ditemukan</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>22</v>
       </c>
       <c r="B12" s="15"/>
     </row>
-    <row r="13" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
         <v>0</v>
       </c>
@@ -904,7 +883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
         <v>2</v>
       </c>
@@ -912,7 +891,7 @@
         <v>5000000</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
         <v>3</v>
       </c>
@@ -920,7 +899,7 @@
         <v>7000000</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
         <v>4</v>
       </c>
